--- a/data/antenas.xlsx
+++ b/data/antenas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hector.andagua\Downloads\Entel\GEO_PROYECTO_MAYO\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24823A5B-AE60-47D1-BA13-3E14D1E2367D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49726BEB-D1C5-42B0-A3C7-A8A2358C13C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D5BFDA3D-8796-45C8-82C2-76AA75EB904A}"/>
   </bookViews>
@@ -20673,6 +20673,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O375" xr:uid="{62FBC65E-14EF-4E55-93FC-E31F4273093C}"/>
   <conditionalFormatting sqref="C249">
     <cfRule type="duplicateValues" dxfId="15" priority="16"/>
     <cfRule type="duplicateValues" dxfId="14" priority="17"/>

--- a/data/antenas.xlsx
+++ b/data/antenas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hector.andagua\Downloads\Entel\GEO_PROYECTO_MAYO\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49726BEB-D1C5-42B0-A3C7-A8A2358C13C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFFF8B3-6569-4349-BA80-16E79FF63EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D5BFDA3D-8796-45C8-82C2-76AA75EB904A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3756" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3866" uniqueCount="680">
   <si>
     <t>N</t>
   </si>
@@ -2004,13 +2004,88 @@
   </si>
   <si>
     <t>Russel</t>
+  </si>
+  <si>
+    <t>Piloto</t>
+  </si>
+  <si>
+    <t>CONDORCANQUI</t>
+  </si>
+  <si>
+    <t>NIEVA</t>
+  </si>
+  <si>
+    <t>REQUENA</t>
+  </si>
+  <si>
+    <t>EMILIO SAN MARTÍN</t>
+  </si>
+  <si>
+    <t>ATALAYA</t>
+  </si>
+  <si>
+    <t>RAIMONDI</t>
+  </si>
+  <si>
+    <t>DATEM DEL MARAï¿½ON</t>
+  </si>
+  <si>
+    <t>ALTO AMAZONAS</t>
+  </si>
+  <si>
+    <t>LAGUNAS</t>
+  </si>
+  <si>
+    <t>YURIMAGUAS</t>
+  </si>
+  <si>
+    <t>NAPO</t>
+  </si>
+  <si>
+    <t>HUANTA</t>
+  </si>
+  <si>
+    <t>CANAYRE</t>
+  </si>
+  <si>
+    <t>SARAYACU</t>
+  </si>
+  <si>
+    <t>01_AMAZONAS_Nieva</t>
+  </si>
+  <si>
+    <t>02_LORETO_Emilio San Martin</t>
+  </si>
+  <si>
+    <t>05_LORETO_Barranca</t>
+  </si>
+  <si>
+    <t>06_LORETO_Lagunas</t>
+  </si>
+  <si>
+    <t>07_LORETO_Yurimaguas</t>
+  </si>
+  <si>
+    <t>08_LORETO_Napo</t>
+  </si>
+  <si>
+    <t>09_AYACUHO_Canayre</t>
+  </si>
+  <si>
+    <t>10_LORETO_Sarayacu</t>
+  </si>
+  <si>
+    <t>04_UCAYALI_Raimondi</t>
+  </si>
+  <si>
+    <t>03_LORETO_Emilio San Martin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2036,6 +2111,12 @@
       <color rgb="FF000000"/>
       <name val="Aptos"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2125,8 +2206,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2161,8 +2243,9 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{99C115D2-9791-4DDF-ACCF-A4B9D8C48387}"/>
   </cellStyles>
   <dxfs count="16">
     <dxf>
@@ -2655,7 +2738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62FBC65E-14EF-4E55-93FC-E31F4273093C}">
-  <dimension ref="A1:O375"/>
+  <dimension ref="A1:O385"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.21875" bestFit="1" customWidth="1"/>
@@ -20672,15 +20755,484 @@
         <v>653</v>
       </c>
     </row>
+    <row r="376" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A376" s="3">
+        <v>376</v>
+      </c>
+      <c r="B376" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="C376" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="D376" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="E376" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F376" s="8">
+        <v>46161</v>
+      </c>
+      <c r="G376" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H376" s="7">
+        <v>-4.7165699999999999</v>
+      </c>
+      <c r="I376" s="7">
+        <v>-78.056539999999998</v>
+      </c>
+      <c r="J376" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="K376" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="L376" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="M376" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="N376" t="s">
+        <v>649</v>
+      </c>
+      <c r="O376" s="10" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="377" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A377" s="3">
+        <v>377</v>
+      </c>
+      <c r="B377" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="C377" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="D377" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="E377" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F377" s="8">
+        <v>46161</v>
+      </c>
+      <c r="G377" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H377" s="7">
+        <v>-5.5640200000000002</v>
+      </c>
+      <c r="I377" s="7">
+        <v>-74.170429999999996</v>
+      </c>
+      <c r="J377" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="K377" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="L377" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="M377" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="N377" t="s">
+        <v>649</v>
+      </c>
+      <c r="O377" s="10" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="378" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A378" s="3">
+        <v>378</v>
+      </c>
+      <c r="B378" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="C378" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="D378" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="E378" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F378" s="8">
+        <v>46161</v>
+      </c>
+      <c r="G378" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H378" s="7">
+        <v>-5.7943908314625796</v>
+      </c>
+      <c r="I378" s="7">
+        <v>-74.283351239992896</v>
+      </c>
+      <c r="J378" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="K378" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="L378" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="M378" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="N378" t="s">
+        <v>649</v>
+      </c>
+      <c r="O378" s="10" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="379" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A379" s="3">
+        <v>379</v>
+      </c>
+      <c r="B379" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="C379" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="D379" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="E379" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F379" s="8">
+        <v>46161</v>
+      </c>
+      <c r="G379" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H379" s="7">
+        <v>-10.7288</v>
+      </c>
+      <c r="I379" s="7">
+        <v>-73.753860000000003</v>
+      </c>
+      <c r="J379" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K379" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="L379" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="M379" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="N379" t="s">
+        <v>649</v>
+      </c>
+      <c r="O379" s="10" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="380" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A380" s="3">
+        <v>380</v>
+      </c>
+      <c r="B380" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="C380" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="D380" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E380" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F380" s="8">
+        <v>46161</v>
+      </c>
+      <c r="G380" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H380" s="7">
+        <v>-4.8272199999999996</v>
+      </c>
+      <c r="I380" s="7">
+        <v>-76.550870000000003</v>
+      </c>
+      <c r="J380" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="K380" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="L380" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="M380" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="N380" t="s">
+        <v>649</v>
+      </c>
+      <c r="O380" s="10" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="381" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A381" s="3">
+        <v>381</v>
+      </c>
+      <c r="B381" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="C381" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="D381" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="E381" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F381" s="8">
+        <v>46161</v>
+      </c>
+      <c r="G381" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H381" s="7">
+        <v>-5.22567</v>
+      </c>
+      <c r="I381" s="7">
+        <v>-75.677700000000002</v>
+      </c>
+      <c r="J381" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="K381" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="L381" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="M381" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="N381" t="s">
+        <v>649</v>
+      </c>
+      <c r="O381" s="10" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="382" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A382" s="3">
+        <v>382</v>
+      </c>
+      <c r="B382" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="C382" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="D382" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="E382" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F382" s="8">
+        <v>46161</v>
+      </c>
+      <c r="G382" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H382" s="7">
+        <v>-6.1093400000000004</v>
+      </c>
+      <c r="I382" s="7">
+        <v>-76.268469999999894</v>
+      </c>
+      <c r="J382" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="K382" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="L382" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="M382" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="N382" t="s">
+        <v>649</v>
+      </c>
+      <c r="O382" s="10" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="383" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A383" s="3">
+        <v>383</v>
+      </c>
+      <c r="B383" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="C383" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="D383" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="E383" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F383" s="8">
+        <v>46161</v>
+      </c>
+      <c r="G383" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H383" s="7">
+        <v>-2.4893420000000002</v>
+      </c>
+      <c r="I383" s="7">
+        <v>-73.680070000000001</v>
+      </c>
+      <c r="J383" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="K383" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="L383" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="M383" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="N383" t="s">
+        <v>649</v>
+      </c>
+      <c r="O383" s="10" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="384" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A384" s="3">
+        <v>384</v>
+      </c>
+      <c r="B384" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="C384" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="D384" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="E384" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F384" s="8">
+        <v>46161</v>
+      </c>
+      <c r="G384" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H384" s="7">
+        <v>-12.282513</v>
+      </c>
+      <c r="I384" s="7">
+        <v>-74.026792999999898</v>
+      </c>
+      <c r="J384" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K384" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="L384" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="M384" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="N384" t="s">
+        <v>649</v>
+      </c>
+      <c r="O384" s="10" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="385" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A385" s="3">
+        <v>385</v>
+      </c>
+      <c r="B385" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="C385" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="D385" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="E385" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F385" s="8">
+        <v>46161</v>
+      </c>
+      <c r="G385" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H385" s="7">
+        <v>-6.0432740000000003</v>
+      </c>
+      <c r="I385" s="7">
+        <v>-74.86224</v>
+      </c>
+      <c r="J385" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="K385" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L385" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="M385" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="N385" t="s">
+        <v>649</v>
+      </c>
+      <c r="O385" s="10" t="s">
+        <v>655</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O375" xr:uid="{62FBC65E-14EF-4E55-93FC-E31F4273093C}"/>
   <conditionalFormatting sqref="C249">
     <cfRule type="duplicateValues" dxfId="15" priority="16"/>
     <cfRule type="duplicateValues" dxfId="14" priority="17"/>
     <cfRule type="duplicateValues" dxfId="13" priority="18"/>
     <cfRule type="duplicateValues" dxfId="12" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:D375">
+  <conditionalFormatting sqref="C1:D375 C377:D385 C376">
     <cfRule type="duplicateValues" dxfId="11" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J89">
